--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260917.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.92%</t>
+          <t>11.09%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>10.37%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>7.64%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>7.61%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.53%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.80%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.29%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -975,39 +975,39 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,536</t>
+          <t>76,601</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>94,663</t>
+          <t>49,536</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,39 +1019,39 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>76,601</t>
+          <t>49,860</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>49,860</t>
+          <t>94,663</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1210,90 +1210,90 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,237</t>
+          <t>74,774</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>74,774</t>
+          <t>30,114</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>30,114</t>
+          <t>11,237</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>202612ESZ6</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13,152</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,88 +1305,88 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>202612ESZ6</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>8,904</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,152</t>
+          <t>8,904</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>30,491</t>
+          <t>10,546</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>30,491</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1408,24 +1408,24 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,546</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1547,44 +1547,44 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,727</t>
+          <t>5,778</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>6,727</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>129,757,485</t>
+          <t>137,799,120</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
